--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/106.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/106.xlsx
@@ -426,13 +426,13 @@
         <v>-41.25696316654456</v>
       </c>
       <c r="E2">
-        <v>-9.677595590455473</v>
+        <v>-11.65741481615594</v>
       </c>
       <c r="F2">
-        <v>-0.8124902320375552</v>
+        <v>-1.81810009454446</v>
       </c>
       <c r="G2">
-        <v>-15.99551985964216</v>
+        <v>-13.61843690943351</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-40.67767696735639</v>
       </c>
       <c r="E3">
-        <v>-13.22608273354368</v>
+        <v>-12.98379684448716</v>
       </c>
       <c r="F3">
-        <v>-0.6612651357172831</v>
+        <v>-1.434605748683623</v>
       </c>
       <c r="G3">
-        <v>-15.00761541173719</v>
+        <v>-13.21318016416107</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-39.74154595346723</v>
       </c>
       <c r="E4">
-        <v>-11.68036546193694</v>
+        <v>-13.73177359124348</v>
       </c>
       <c r="F4">
-        <v>-0.5036856330501359</v>
+        <v>-1.699206177955452</v>
       </c>
       <c r="G4">
-        <v>-14.91384921437506</v>
+        <v>-12.49165651374886</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-38.57622058164615</v>
       </c>
       <c r="E5">
-        <v>-12.4165553949534</v>
+        <v>-13.42399986601706</v>
       </c>
       <c r="F5">
-        <v>-0.7835379629423097</v>
+        <v>-1.653533312834699</v>
       </c>
       <c r="G5">
-        <v>-14.57823147032597</v>
+        <v>-12.27796967971083</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-37.20997498706585</v>
       </c>
       <c r="E6">
-        <v>-12.15158881885199</v>
+        <v>-15.02405775459785</v>
       </c>
       <c r="F6">
-        <v>-0.8428755767396439</v>
+        <v>-1.35685187078725</v>
       </c>
       <c r="G6">
-        <v>-13.71624584479498</v>
+        <v>-12.39033090542316</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-35.73470389200814</v>
       </c>
       <c r="E7">
-        <v>-13.38461080981239</v>
+        <v>-15.34558276252078</v>
       </c>
       <c r="F7">
-        <v>-0.5601612374707978</v>
+        <v>-1.158534915985229</v>
       </c>
       <c r="G7">
-        <v>-13.71377608041179</v>
+        <v>-11.69500216086589</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-34.21084871193261</v>
       </c>
       <c r="E8">
-        <v>-14.95931749646643</v>
+        <v>-16.19436625455334</v>
       </c>
       <c r="F8">
-        <v>-0.4737244124582806</v>
+        <v>-1.193233569753695</v>
       </c>
       <c r="G8">
-        <v>-12.88730310818142</v>
+        <v>-11.33719830928152</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-32.67476709663445</v>
       </c>
       <c r="E9">
-        <v>-14.91073323038858</v>
+        <v>-16.05193602537967</v>
       </c>
       <c r="F9">
-        <v>-0.1040795412048488</v>
+        <v>-0.9276987420515077</v>
       </c>
       <c r="G9">
-        <v>-12.88438037961167</v>
+        <v>-9.805910452022074</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-31.18336653024435</v>
       </c>
       <c r="E10">
-        <v>-14.89050709123667</v>
+        <v>-17.80288008139149</v>
       </c>
       <c r="F10">
-        <v>0.2260538616698521</v>
+        <v>-0.9668772067343131</v>
       </c>
       <c r="G10">
-        <v>-11.11004917075942</v>
+        <v>-9.629180013043547</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-29.72948377060135</v>
       </c>
       <c r="E11">
-        <v>-15.84786383372289</v>
+        <v>-16.99724430181257</v>
       </c>
       <c r="F11">
-        <v>-0.5053258005076789</v>
+        <v>-0.6895886739538037</v>
       </c>
       <c r="G11">
-        <v>-10.26889076020404</v>
+        <v>-8.904903332460012</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-28.36391687678386</v>
       </c>
       <c r="E12">
-        <v>-16.92768216533302</v>
+        <v>-18.47547188939084</v>
       </c>
       <c r="F12">
-        <v>0.2296539464024188</v>
+        <v>-0.6523668130764108</v>
       </c>
       <c r="G12">
-        <v>-10.79139996118027</v>
+        <v>-7.740033478563314</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-27.07170564219354</v>
       </c>
       <c r="E13">
-        <v>-19.25794936262252</v>
+        <v>-18.34487415928161</v>
       </c>
       <c r="F13">
-        <v>0.6137240076082011</v>
+        <v>-0.4613800814217624</v>
       </c>
       <c r="G13">
-        <v>-8.852069694169654</v>
+        <v>-7.338905625861712</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-25.89254841629858</v>
       </c>
       <c r="E14">
-        <v>-18.81034947172309</v>
+        <v>-20.12168026221313</v>
       </c>
       <c r="F14">
-        <v>0.06382970297520815</v>
+        <v>-0.4900796984591541</v>
       </c>
       <c r="G14">
-        <v>-8.099017386702869</v>
+        <v>-6.504224472636884</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-24.81638706613059</v>
       </c>
       <c r="E15">
-        <v>-19.11441437923644</v>
+        <v>-21.49168762230035</v>
       </c>
       <c r="F15">
-        <v>0.6299417846202099</v>
+        <v>-0.3374256683690527</v>
       </c>
       <c r="G15">
-        <v>-8.060397947338824</v>
+        <v>-6.108446035602475</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-23.8254057733489</v>
       </c>
       <c r="E16">
-        <v>-20.38132657460744</v>
+        <v>-22.0469844360639</v>
       </c>
       <c r="F16">
-        <v>1.166452985493574</v>
+        <v>-0.2582950438492272</v>
       </c>
       <c r="G16">
-        <v>-7.11773378708096</v>
+        <v>-5.344241932614749</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-22.91138390509292</v>
       </c>
       <c r="E17">
-        <v>-19.9812477276867</v>
+        <v>-24.01453507551082</v>
       </c>
       <c r="F17">
-        <v>0.7165268873978282</v>
+        <v>0.1786372831662056</v>
       </c>
       <c r="G17">
-        <v>-7.781343290228499</v>
+        <v>-4.623715586636349</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-22.02894355124681</v>
       </c>
       <c r="E18">
-        <v>-21.92885879956313</v>
+        <v>-23.84337708360331</v>
       </c>
       <c r="F18">
-        <v>0.4765571344808394</v>
+        <v>0.4087635462357279</v>
       </c>
       <c r="G18">
-        <v>-6.833922353325625</v>
+        <v>-4.68297948885462</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-21.18067817124071</v>
       </c>
       <c r="E19">
-        <v>-24.41021982484989</v>
+        <v>-25.03720937250263</v>
       </c>
       <c r="F19">
-        <v>1.280983062604634</v>
+        <v>0.5348824833119527</v>
       </c>
       <c r="G19">
-        <v>-5.900975384435884</v>
+        <v>-3.989537007264429</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-20.32455340027064</v>
       </c>
       <c r="E20">
-        <v>-22.37815320068308</v>
+        <v>-25.87620374544257</v>
       </c>
       <c r="F20">
-        <v>1.564538194787321</v>
+        <v>0.647914043791348</v>
       </c>
       <c r="G20">
-        <v>-6.111740795276459</v>
+        <v>-4.090053284766882</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-19.47647729240155</v>
       </c>
       <c r="E21">
-        <v>-24.82633006748446</v>
+        <v>-26.76586729654541</v>
       </c>
       <c r="F21">
-        <v>1.50751835298302</v>
+        <v>0.3627709312974937</v>
       </c>
       <c r="G21">
-        <v>-6.089494640615583</v>
+        <v>-3.743359456789993</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-18.62643798338044</v>
       </c>
       <c r="E22">
-        <v>-23.91553913037221</v>
+        <v>-26.92449504988592</v>
       </c>
       <c r="F22">
-        <v>1.900760926440001</v>
+        <v>0.5315557598223098</v>
       </c>
       <c r="G22">
-        <v>-6.605095811403728</v>
+        <v>-3.703670917515889</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.79375544452637</v>
       </c>
       <c r="E23">
-        <v>-25.66634197719898</v>
+        <v>-25.92549405744563</v>
       </c>
       <c r="F23">
-        <v>1.928605668317704</v>
+        <v>0.7308162250961197</v>
       </c>
       <c r="G23">
-        <v>-6.053176572608606</v>
+        <v>-3.220936410385269</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.00763699608876</v>
       </c>
       <c r="E24">
-        <v>-27.33156790467766</v>
+        <v>-26.8897492839424</v>
       </c>
       <c r="F24">
-        <v>2.019141255239273</v>
+        <v>0.3280540534461664</v>
       </c>
       <c r="G24">
-        <v>-5.373072385134413</v>
+        <v>-3.398547975663297</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.28159782636271</v>
       </c>
       <c r="E25">
-        <v>-25.5567304239141</v>
+        <v>-26.67938913033983</v>
       </c>
       <c r="F25">
-        <v>1.668254763822236</v>
+        <v>0.3959950910889763</v>
       </c>
       <c r="G25">
-        <v>-6.437219712705962</v>
+        <v>-3.645260728778912</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-15.66302082873819</v>
       </c>
       <c r="E26">
-        <v>-25.24908544823876</v>
+        <v>-27.1768773956731</v>
       </c>
       <c r="F26">
-        <v>1.263975023090354</v>
+        <v>0.2804187859481809</v>
       </c>
       <c r="G26">
-        <v>-6.615081909464736</v>
+        <v>-4.051688393000473</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-15.1575936358033</v>
       </c>
       <c r="E27">
-        <v>-25.19724506448225</v>
+        <v>-26.65074858504381</v>
       </c>
       <c r="F27">
-        <v>0.9017150472328801</v>
+        <v>0.1119147739729139</v>
       </c>
       <c r="G27">
-        <v>-5.861391274945424</v>
+        <v>-4.091888638214435</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-14.80658979008622</v>
       </c>
       <c r="E28">
-        <v>-25.3849037649833</v>
+        <v>-26.2672825834224</v>
       </c>
       <c r="F28">
-        <v>1.235495751782107</v>
+        <v>0.2761618058651942</v>
       </c>
       <c r="G28">
-        <v>-5.416337644498342</v>
+        <v>-4.235382993175794</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-14.60963558420529</v>
       </c>
       <c r="E29">
-        <v>-25.52848858690527</v>
+        <v>-26.16826171901583</v>
       </c>
       <c r="F29">
-        <v>1.245202561008112</v>
+        <v>-0.3711451918674095</v>
       </c>
       <c r="G29">
-        <v>-5.738947353622211</v>
+        <v>-4.361474124692792</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-14.58254650887176</v>
       </c>
       <c r="E30">
-        <v>-24.83122255042511</v>
+        <v>-25.7863324055846</v>
       </c>
       <c r="F30">
-        <v>0.5698851479172458</v>
+        <v>0.1520508313733555</v>
       </c>
       <c r="G30">
-        <v>-6.487855104050603</v>
+        <v>-4.038835697378421</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-14.72849101429976</v>
       </c>
       <c r="E31">
-        <v>-25.003331627726</v>
+        <v>-25.89988950962806</v>
       </c>
       <c r="F31">
-        <v>0.6538658635804624</v>
+        <v>-0.02795174852017147</v>
       </c>
       <c r="G31">
-        <v>-6.024667241673649</v>
+        <v>-4.837901072891283</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.02765464059906</v>
       </c>
       <c r="E32">
-        <v>-22.65106071683756</v>
+        <v>-24.64127543048407</v>
       </c>
       <c r="F32">
-        <v>1.004682772135664</v>
+        <v>-0.1125976432078361</v>
       </c>
       <c r="G32">
-        <v>-5.670339596512345</v>
+        <v>-4.441080948765019</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.48862723454191</v>
       </c>
       <c r="E33">
-        <v>-23.49247641197988</v>
+        <v>-24.43091112367018</v>
       </c>
       <c r="F33">
-        <v>0.8974125069427394</v>
+        <v>0.2760839393293311</v>
       </c>
       <c r="G33">
-        <v>-5.936202161203775</v>
+        <v>-4.677295897879767</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-16.07539749945262</v>
       </c>
       <c r="E34">
-        <v>-22.26869946942855</v>
+        <v>-24.05444743634242</v>
       </c>
       <c r="F34">
-        <v>0.7326933056308633</v>
+        <v>0.2880058029904216</v>
       </c>
       <c r="G34">
-        <v>-6.205184565681586</v>
+        <v>-4.080957450611443</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.78772141717134</v>
       </c>
       <c r="E35">
-        <v>-23.38657367640807</v>
+        <v>-22.6252235891858</v>
       </c>
       <c r="F35">
-        <v>1.50832021262893</v>
+        <v>-0.09511080733473859</v>
       </c>
       <c r="G35">
-        <v>-5.898009578580379</v>
+        <v>-5.505943620354532</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-17.58441364632196</v>
       </c>
       <c r="E36">
-        <v>-22.25535520144187</v>
+        <v>-22.27266993945508</v>
       </c>
       <c r="F36">
-        <v>1.151752777563494</v>
+        <v>0.3734187658930786</v>
       </c>
       <c r="G36">
-        <v>-6.813253088397781</v>
+        <v>-5.55436248954132</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-18.44916555200492</v>
       </c>
       <c r="E37">
-        <v>-21.6164667033435</v>
+        <v>-21.79780006299683</v>
       </c>
       <c r="F37">
-        <v>1.589778549550622</v>
+        <v>0.3978630595822892</v>
       </c>
       <c r="G37">
-        <v>-6.307544028865364</v>
+        <v>-6.029011520673262</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-19.35136122606517</v>
       </c>
       <c r="E38">
-        <v>-21.55734989334589</v>
+        <v>-20.59102636760936</v>
       </c>
       <c r="F38">
-        <v>1.375334109783497</v>
+        <v>0.3049856780130058</v>
       </c>
       <c r="G38">
-        <v>-6.557013728269195</v>
+        <v>-6.601224077175107</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-20.25153654165223</v>
       </c>
       <c r="E39">
-        <v>-20.36482171280257</v>
+        <v>-20.78685028157502</v>
       </c>
       <c r="F39">
-        <v>1.883772767743389</v>
+        <v>0.6134481612630689</v>
       </c>
       <c r="G39">
-        <v>-7.092339074443201</v>
+        <v>-6.170511266767011</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-21.13733124533189</v>
       </c>
       <c r="E40">
-        <v>-20.2956582846102</v>
+        <v>-20.21639424647585</v>
       </c>
       <c r="F40">
-        <v>1.773596589701444</v>
+        <v>0.9785941691518966</v>
       </c>
       <c r="G40">
-        <v>-7.494960273050919</v>
+        <v>-6.808169968678884</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-21.96348655162389</v>
       </c>
       <c r="E41">
-        <v>-20.69210722483303</v>
+        <v>-19.82659875079539</v>
       </c>
       <c r="F41">
-        <v>1.518626759854562</v>
+        <v>1.168283677453761</v>
       </c>
       <c r="G41">
-        <v>-7.368780376217822</v>
+        <v>-7.362355333779092</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-22.73010958648925</v>
       </c>
       <c r="E42">
-        <v>-18.98695232367745</v>
+        <v>-19.06778212248127</v>
       </c>
       <c r="F42">
-        <v>2.525306873045883</v>
+        <v>0.9837085094967808</v>
       </c>
       <c r="G42">
-        <v>-7.212973749764772</v>
+        <v>-7.310223985783742</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-23.40352009996132</v>
       </c>
       <c r="E43">
-        <v>-18.35111643590283</v>
+        <v>-18.87864072553725</v>
       </c>
       <c r="F43">
-        <v>2.047927022486556</v>
+        <v>1.2612662616832</v>
       </c>
       <c r="G43">
-        <v>-8.049349276229233</v>
+        <v>-7.771537333544278</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-23.99043015253596</v>
       </c>
       <c r="E44">
-        <v>-17.55959326840568</v>
+        <v>-17.78350119734984</v>
       </c>
       <c r="F44">
-        <v>1.888858943596578</v>
+        <v>0.9861405961914002</v>
       </c>
       <c r="G44">
-        <v>-7.468800612247963</v>
+        <v>-8.318630610962726</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-24.48155347185126</v>
       </c>
       <c r="E45">
-        <v>-15.40157635760212</v>
+        <v>-17.4506836078347</v>
       </c>
       <c r="F45">
-        <v>1.343390605996743</v>
+        <v>1.014091369096661</v>
       </c>
       <c r="G45">
-        <v>-8.827210184173072</v>
+        <v>-8.0198635268172</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-24.88038240273603</v>
       </c>
       <c r="E46">
-        <v>-16.68074052638136</v>
+        <v>-16.59770952557539</v>
       </c>
       <c r="F46">
-        <v>1.750778381223929</v>
+        <v>1.151809106546885</v>
       </c>
       <c r="G46">
-        <v>-8.391005672517569</v>
+        <v>-8.766980306456089</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-25.20646881679098</v>
       </c>
       <c r="E47">
-        <v>-15.62026785312229</v>
+        <v>-15.67750325838975</v>
       </c>
       <c r="F47">
-        <v>1.804433394638058</v>
+        <v>1.212374360835168</v>
       </c>
       <c r="G47">
-        <v>-9.261527127489201</v>
+        <v>-8.654549896012091</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-25.45241652191011</v>
       </c>
       <c r="E48">
-        <v>-14.7758452329808</v>
+        <v>-15.4225334619472</v>
       </c>
       <c r="F48">
-        <v>2.073455649106031</v>
+        <v>1.252144279843572</v>
       </c>
       <c r="G48">
-        <v>-9.165483055471325</v>
+        <v>-8.802530815553279</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-25.65412109394396</v>
       </c>
       <c r="E49">
-        <v>-15.71832932571282</v>
+        <v>-15.55789492544602</v>
       </c>
       <c r="F49">
-        <v>2.269434122729949</v>
+        <v>1.477859486493187</v>
       </c>
       <c r="G49">
-        <v>-8.536529881398518</v>
+        <v>-9.051261674237823</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-25.80084716427189</v>
       </c>
       <c r="E50">
-        <v>-13.98507794994477</v>
+        <v>-14.53696497721064</v>
       </c>
       <c r="F50">
-        <v>1.619690896465712</v>
+        <v>1.512165494112725</v>
       </c>
       <c r="G50">
-        <v>-9.099781057091368</v>
+        <v>-9.471488428995713</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-25.92633081639682</v>
       </c>
       <c r="E51">
-        <v>-13.38296198491643</v>
+        <v>-14.24724110840192</v>
       </c>
       <c r="F51">
-        <v>2.107093992598914</v>
+        <v>1.197119146745212</v>
       </c>
       <c r="G51">
-        <v>-8.973068568361684</v>
+        <v>-9.305677429269517</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-26.021670154921</v>
       </c>
       <c r="E52">
-        <v>-13.88802155449485</v>
+        <v>-13.4338429768569</v>
       </c>
       <c r="F52">
-        <v>1.83549717224304</v>
+        <v>1.544778318760942</v>
       </c>
       <c r="G52">
-        <v>-10.74480078097348</v>
+        <v>-9.855746955521836</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-26.10522407161547</v>
       </c>
       <c r="E53">
-        <v>-12.9343736297217</v>
+        <v>-12.22663734749164</v>
       </c>
       <c r="F53">
-        <v>1.543822382778111</v>
+        <v>0.996230111157498</v>
       </c>
       <c r="G53">
-        <v>-9.344765497287666</v>
+        <v>-9.607044815027793</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-26.18227901377789</v>
       </c>
       <c r="E54">
-        <v>-13.27926460455811</v>
+        <v>-12.41684196653481</v>
       </c>
       <c r="F54">
-        <v>1.938110355897426</v>
+        <v>1.626816512864594</v>
       </c>
       <c r="G54">
-        <v>-9.025874793833838</v>
+        <v>-9.701102110411831</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-26.240243639502</v>
       </c>
       <c r="E55">
-        <v>-11.74977392959748</v>
+        <v>-12.16543147219764</v>
       </c>
       <c r="F55">
-        <v>1.853492625701456</v>
+        <v>1.266145345685689</v>
       </c>
       <c r="G55">
-        <v>-9.499903773125391</v>
+        <v>-10.16411244215659</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-26.29962863816163</v>
       </c>
       <c r="E56">
-        <v>-11.14491269188342</v>
+        <v>-11.35722900801998</v>
       </c>
       <c r="F56">
-        <v>1.574329497488411</v>
+        <v>1.176562381277339</v>
       </c>
       <c r="G56">
-        <v>-9.301803084296305</v>
+        <v>-10.13561616494459</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-26.33294963789371</v>
       </c>
       <c r="E57">
-        <v>-10.98582808529719</v>
+        <v>-10.78124920185879</v>
       </c>
       <c r="F57">
-        <v>1.637235718057006</v>
+        <v>1.287764078163951</v>
       </c>
       <c r="G57">
-        <v>-9.694763222544609</v>
+        <v>-9.805171611302789</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-26.36053409540559</v>
       </c>
       <c r="E58">
-        <v>-10.56995042249681</v>
+        <v>-10.74571847897488</v>
       </c>
       <c r="F58">
-        <v>1.336283213680723</v>
+        <v>1.404557255019458</v>
       </c>
       <c r="G58">
-        <v>-10.30747756526069</v>
+        <v>-10.49700065273567</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-26.35251708871144</v>
       </c>
       <c r="E59">
-        <v>-10.12675293560171</v>
+        <v>-10.05594068251338</v>
       </c>
       <c r="F59">
-        <v>1.424676642498653</v>
+        <v>1.12427748754744</v>
       </c>
       <c r="G59">
-        <v>-9.914790249822158</v>
+        <v>-10.93508098437989</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-26.32202785148074</v>
       </c>
       <c r="E60">
-        <v>-10.3395427178293</v>
+        <v>-9.281213101613837</v>
       </c>
       <c r="F60">
-        <v>1.723876321450612</v>
+        <v>1.234379112523134</v>
       </c>
       <c r="G60">
-        <v>-10.72204161500045</v>
+        <v>-10.67489548380184</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-26.25472198521772</v>
       </c>
       <c r="E61">
-        <v>-10.99925541751036</v>
+        <v>-9.210600202669102</v>
       </c>
       <c r="F61">
-        <v>2.33159646937083</v>
+        <v>1.08269510066171</v>
       </c>
       <c r="G61">
-        <v>-11.7494962327162</v>
+        <v>-10.81425703007546</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-26.14437703809422</v>
       </c>
       <c r="E62">
-        <v>-9.514615271646552</v>
+        <v>-9.449592595145036</v>
       </c>
       <c r="F62">
-        <v>1.633571020667021</v>
+        <v>0.8718590293011803</v>
       </c>
       <c r="G62">
-        <v>-10.48322114278378</v>
+        <v>-10.72595773188712</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-26.00159809861985</v>
       </c>
       <c r="E63">
-        <v>-7.641836761420891</v>
+        <v>-8.157889881376137</v>
       </c>
       <c r="F63">
-        <v>1.957277120863401</v>
+        <v>1.134158253928033</v>
       </c>
       <c r="G63">
-        <v>-10.22482269687834</v>
+        <v>-11.10524931682865</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-25.80655901403644</v>
       </c>
       <c r="E64">
-        <v>-10.93985618914266</v>
+        <v>-8.653613031896347</v>
       </c>
       <c r="F64">
-        <v>1.97820002472331</v>
+        <v>0.8404788153483295</v>
       </c>
       <c r="G64">
-        <v>-10.93366465543921</v>
+        <v>-11.07717598024041</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-25.58630485333198</v>
       </c>
       <c r="E65">
-        <v>-9.793059018497031</v>
+        <v>-8.136666971506264</v>
       </c>
       <c r="F65">
-        <v>1.631872867491282</v>
+        <v>0.8551392616430751</v>
       </c>
       <c r="G65">
-        <v>-10.79311652574892</v>
+        <v>-10.57204128451804</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-25.32240847416542</v>
       </c>
       <c r="E66">
-        <v>-8.984324943269794</v>
+        <v>-7.735163573101113</v>
       </c>
       <c r="F66">
-        <v>1.58761485389451</v>
+        <v>0.7830215955553501</v>
       </c>
       <c r="G66">
-        <v>-10.7539344709255</v>
+        <v>-10.81870443348642</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-25.04627341265236</v>
       </c>
       <c r="E67">
-        <v>-8.456597146280455</v>
+        <v>-8.056140357129163</v>
       </c>
       <c r="F67">
-        <v>1.63692922211797</v>
+        <v>0.4758629625972934</v>
       </c>
       <c r="G67">
-        <v>-10.7337220863011</v>
+        <v>-10.54917377264448</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-24.75092427600195</v>
       </c>
       <c r="E68">
-        <v>-9.312088074602613</v>
+        <v>-8.20772841727408</v>
       </c>
       <c r="F68">
-        <v>1.042827434299776</v>
+        <v>0.7321333292665709</v>
       </c>
       <c r="G68">
-        <v>-11.16817609370826</v>
+        <v>-10.40115760805131</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-24.45559827771369</v>
       </c>
       <c r="E69">
-        <v>-9.797083480270791</v>
+        <v>-8.366900241298133</v>
       </c>
       <c r="F69">
-        <v>0.6755964256581019</v>
+        <v>0.4734275624330629</v>
       </c>
       <c r="G69">
-        <v>-11.39098748009223</v>
+        <v>-10.49230522858855</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-24.17494867952549</v>
       </c>
       <c r="E70">
-        <v>-10.23543832276114</v>
+        <v>-7.567726858540651</v>
       </c>
       <c r="F70">
-        <v>1.102832712223766</v>
+        <v>0.5297466054145957</v>
       </c>
       <c r="G70">
-        <v>-9.353589814005629</v>
+        <v>-9.701305748489938</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-23.90288414368653</v>
       </c>
       <c r="E71">
-        <v>-7.725806387986275</v>
+        <v>-8.081018092964886</v>
       </c>
       <c r="F71">
-        <v>1.610505958703472</v>
+        <v>0.4391894809405537</v>
       </c>
       <c r="G71">
-        <v>-10.28999993559548</v>
+        <v>-9.803851879911981</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-23.66601298998253</v>
       </c>
       <c r="E72">
-        <v>-9.141673507522247</v>
+        <v>-7.901669968324814</v>
       </c>
       <c r="F72">
-        <v>1.214996972032431</v>
+        <v>0.6742528137307611</v>
       </c>
       <c r="G72">
-        <v>-10.81569685571746</v>
+        <v>-9.27009689660953</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-23.44174790187539</v>
       </c>
       <c r="E73">
-        <v>-7.762877952271694</v>
+        <v>-7.696949875701366</v>
       </c>
       <c r="F73">
-        <v>1.086671264195148</v>
+        <v>0.4924294822858807</v>
       </c>
       <c r="G73">
-        <v>-10.53106173204363</v>
+        <v>-9.397676152543463</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-23.25045959497392</v>
       </c>
       <c r="E74">
-        <v>-9.106288147034709</v>
+        <v>-7.639747696124503</v>
       </c>
       <c r="F74">
-        <v>1.425567965824065</v>
+        <v>-0.008090811670650523</v>
       </c>
       <c r="G74">
-        <v>-9.872932181792839</v>
+        <v>-8.906790900799388</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-23.06232406815255</v>
       </c>
       <c r="E75">
-        <v>-9.775295733660741</v>
+        <v>-8.148117375128816</v>
       </c>
       <c r="F75">
-        <v>1.341554943832139</v>
+        <v>0.2799656689788496</v>
       </c>
       <c r="G75">
-        <v>-10.13386174457936</v>
+        <v>-8.927756485238323</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-22.88563035174544</v>
       </c>
       <c r="E76">
-        <v>-8.597270567063722</v>
+        <v>-7.74637724367815</v>
       </c>
       <c r="F76">
-        <v>1.649982635651285</v>
+        <v>0.4804479761717887</v>
       </c>
       <c r="G76">
-        <v>-9.045134256682481</v>
+        <v>-8.849085613102011</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-22.70645248676596</v>
       </c>
       <c r="E77">
-        <v>-9.29134693724642</v>
+        <v>-8.848510779736575</v>
       </c>
       <c r="F77">
-        <v>0.9943033285785864</v>
+        <v>0.2137285830835983</v>
       </c>
       <c r="G77">
-        <v>-8.501411450531158</v>
+        <v>-8.123070176620795</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-22.51007935574061</v>
       </c>
       <c r="E78">
-        <v>-10.56634128185553</v>
+        <v>-9.04765310955078</v>
       </c>
       <c r="F78">
-        <v>1.00233517891613</v>
+        <v>0.1874105223292552</v>
       </c>
       <c r="G78">
-        <v>-8.937788271329676</v>
+        <v>-7.987563394735946</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-22.303322300238</v>
       </c>
       <c r="E79">
-        <v>-11.90203065676569</v>
+        <v>-9.460258041827196</v>
       </c>
       <c r="F79">
-        <v>0.8999870728306403</v>
+        <v>0.380490538410778</v>
       </c>
       <c r="G79">
-        <v>-8.824732587556106</v>
+        <v>-7.630823421572454</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-22.06186596666814</v>
       </c>
       <c r="E80">
-        <v>-12.47887017767113</v>
+        <v>-10.15433441200989</v>
       </c>
       <c r="F80">
-        <v>1.259261612568425</v>
+        <v>0.1403112085408809</v>
       </c>
       <c r="G80">
-        <v>-8.472339504136817</v>
+        <v>-7.423731328371574</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-21.80444594554638</v>
       </c>
       <c r="E81">
-        <v>-12.59800089131251</v>
+        <v>-11.18045172118998</v>
       </c>
       <c r="F81">
-        <v>0.7256936010772076</v>
+        <v>0.2264224851640979</v>
       </c>
       <c r="G81">
-        <v>-7.961398512443809</v>
+        <v>-7.086425737944329</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-21.50920643803962</v>
       </c>
       <c r="E82">
-        <v>-12.848929613136</v>
+        <v>-11.18347525903446</v>
       </c>
       <c r="F82">
-        <v>1.018503253883971</v>
+        <v>0.04518149600338568</v>
       </c>
       <c r="G82">
-        <v>-7.873753205775545</v>
+        <v>-6.722198149293523</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-21.19574374406748</v>
       </c>
       <c r="E83">
-        <v>-13.14127415829068</v>
+        <v>-12.91779401011298</v>
       </c>
       <c r="F83">
-        <v>0.9345697551627141</v>
+        <v>0.1944508168856482</v>
       </c>
       <c r="G83">
-        <v>-6.981385040065477</v>
+        <v>-6.630780316691101</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-20.85548165631141</v>
       </c>
       <c r="E84">
-        <v>-14.80203953680649</v>
+        <v>-13.12530506074672</v>
       </c>
       <c r="F84">
-        <v>0.8165721321035357</v>
+        <v>-0.04888624952372057</v>
       </c>
       <c r="G84">
-        <v>-7.90589408243674</v>
+        <v>-6.421184519427344</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-20.49600397654607</v>
       </c>
       <c r="E85">
-        <v>-16.16318809713785</v>
+        <v>-15.44714123904681</v>
       </c>
       <c r="F85">
-        <v>0.4730324311819276</v>
+        <v>0.01983179674291521</v>
       </c>
       <c r="G85">
-        <v>-7.901929666775135</v>
+        <v>-6.293788015614789</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-20.13118386471904</v>
       </c>
       <c r="E86">
-        <v>-15.38579000135645</v>
+        <v>-15.35245217405205</v>
       </c>
       <c r="F86">
-        <v>0.8647201590238541</v>
+        <v>0.1749518765911506</v>
       </c>
       <c r="G86">
-        <v>-6.462945989906792</v>
+        <v>-6.003851775048703</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-19.75574697312846</v>
       </c>
       <c r="E87">
-        <v>-18.35777818686785</v>
+        <v>-17.29007477269225</v>
       </c>
       <c r="F87">
-        <v>1.165091149483372</v>
+        <v>-0.3386226592660981</v>
       </c>
       <c r="G87">
-        <v>-7.588793044400121</v>
+        <v>-5.455477927408313</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-19.40050210454645</v>
       </c>
       <c r="E88">
-        <v>-18.98583095661975</v>
+        <v>-18.00284890025933</v>
       </c>
       <c r="F88">
-        <v>0.4246483195518112</v>
+        <v>0.28455813785997</v>
       </c>
       <c r="G88">
-        <v>-7.28615814214286</v>
+        <v>-5.93276381057728</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-19.05911416454331</v>
       </c>
       <c r="E89">
-        <v>-21.06627418629816</v>
+        <v>-19.27501075474491</v>
       </c>
       <c r="F89">
-        <v>0.8959562370486179</v>
+        <v>-0.313605963701553</v>
       </c>
       <c r="G89">
-        <v>-5.544927258589036</v>
+        <v>-5.46208572196842</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-18.76629905486263</v>
       </c>
       <c r="E90">
-        <v>-22.81723070194395</v>
+        <v>-21.53870197449741</v>
       </c>
       <c r="F90">
-        <v>0.1651995071579921</v>
+        <v>-0.05541544139258628</v>
       </c>
       <c r="G90">
-        <v>-5.825308173951647</v>
+        <v>-5.544966419757903</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-18.51912392407342</v>
       </c>
       <c r="E91">
-        <v>-23.93429503271513</v>
+        <v>-22.65556279791367</v>
       </c>
       <c r="F91">
-        <v>0.009937776483877917</v>
+        <v>-0.08514554747906053</v>
       </c>
       <c r="G91">
-        <v>-6.303951644307993</v>
+        <v>-5.176222242964471</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-18.33826352102541</v>
       </c>
       <c r="E92">
-        <v>-24.66812594169909</v>
+        <v>-24.74990682589629</v>
       </c>
       <c r="F92">
-        <v>0.7695506848510245</v>
+        <v>-0.4594243059837528</v>
       </c>
       <c r="G92">
-        <v>-5.913084017849467</v>
+        <v>-5.498223648598611</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-18.22805258670278</v>
       </c>
       <c r="E93">
-        <v>-28.07211455637386</v>
+        <v>-27.42097408486724</v>
       </c>
       <c r="F93">
-        <v>0.03437295813165774</v>
+        <v>-0.5595416186535038</v>
       </c>
       <c r="G93">
-        <v>-6.763622833720718</v>
+        <v>-5.032709612790974</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-18.17445062651761</v>
       </c>
       <c r="E94">
-        <v>-30.30625152433888</v>
+        <v>-28.96850215661161</v>
       </c>
       <c r="F94">
-        <v>-0.08403387842450361</v>
+        <v>-0.6182496732247104</v>
       </c>
       <c r="G94">
-        <v>-6.548622795153356</v>
+        <v>-5.581563837436128</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.18279646983349</v>
       </c>
       <c r="E95">
-        <v>-32.79387974551481</v>
+        <v>-30.98011836821496</v>
       </c>
       <c r="F95">
-        <v>-0.5213505679148354</v>
+        <v>-0.6665269254598656</v>
       </c>
       <c r="G95">
-        <v>-6.275833925061702</v>
+        <v>-5.818157344516588</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.21780317133411</v>
       </c>
       <c r="E96">
-        <v>-33.948381123168</v>
+        <v>-33.11242897752349</v>
       </c>
       <c r="F96">
-        <v>-0.2255977257259251</v>
+        <v>-1.040432090265895</v>
       </c>
       <c r="G96">
-        <v>-6.177192162175669</v>
+        <v>-6.191775781461629</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.27514557680585</v>
       </c>
       <c r="E97">
-        <v>-36.63386002543611</v>
+        <v>-36.18292095263152</v>
       </c>
       <c r="F97">
-        <v>-0.6787784793472702</v>
+        <v>-1.32988354162171</v>
       </c>
       <c r="G97">
-        <v>-6.481364792997097</v>
+        <v>-5.981258391357208</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.3144417133976</v>
       </c>
       <c r="E98">
-        <v>-38.55669096194293</v>
+        <v>-38.74943526971124</v>
       </c>
       <c r="F98">
-        <v>-0.369949029337767</v>
+        <v>-1.260404225711901</v>
       </c>
       <c r="G98">
-        <v>-7.444698218182805</v>
+        <v>-6.48827021244059</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.32614000718542</v>
       </c>
       <c r="E99">
-        <v>-42.72407512041745</v>
+        <v>-40.63498905797208</v>
       </c>
       <c r="F99">
-        <v>-0.5817965372971153</v>
+        <v>-1.650397942215103</v>
       </c>
       <c r="G99">
-        <v>-8.031904280871414</v>
+        <v>-6.682517442253193</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.29401812346746</v>
       </c>
       <c r="E100">
-        <v>-43.6458388418499</v>
+        <v>-43.94550134535893</v>
       </c>
       <c r="F100">
-        <v>-1.215626825753574</v>
+        <v>-2.049913742013485</v>
       </c>
       <c r="G100">
-        <v>-6.538738516131402</v>
+        <v>-7.214686398216543</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.20461314518102</v>
       </c>
       <c r="E101">
-        <v>-45.943666343784</v>
+        <v>-45.3767997215723</v>
       </c>
       <c r="F101">
-        <v>-1.323838116316079</v>
+        <v>-2.133201942527961</v>
       </c>
       <c r="G101">
-        <v>-7.851180708040779</v>
+        <v>-6.996031317221623</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.08251635645292</v>
       </c>
       <c r="E102">
-        <v>-47.71729212514353</v>
+        <v>-48.36576415837395</v>
       </c>
       <c r="F102">
-        <v>-1.358451448242056</v>
+        <v>-2.104266240780771</v>
       </c>
       <c r="G102">
-        <v>-8.490399329845843</v>
+        <v>-8.053552575020925</v>
       </c>
     </row>
   </sheetData>
